--- a/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/mobile/mobile_image_text_ratio.xlsx
+++ b/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/mobile/mobile_image_text_ratio.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="C2" t="n">
-        <v>83</v>
+        <v>82.59</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C3" t="n">
-        <v>11.5</v>
+        <v>12.05</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" t="n">
-        <v>5.5</v>
+        <v>5.36</v>
       </c>
     </row>
   </sheetData>
